--- a/filer_2/11142141_nordic_seafood_a_s.xlsx
+++ b/filer_2/11142141_nordic_seafood_a_s.xlsx
@@ -6687,20 +6687,20 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>SUM(B5:B8)</f>
+        <f>IF(COUNT('res_raw_11142141'!$F$2,'res_raw_11142141'!$F$3,'res_raw_11142141'!$F$4,'res_raw_11142141'!$F$5)=0,'res_raw_11142141'!$F$6,SUM(B5:B8))</f>
         <v/>
       </c>
       <c r="C9" s="27">
-        <f>SUM(C5:C8)</f>
+        <f>IF(COUNT('res_raw_11142141'!$E$2,'res_raw_11142141'!$E$3,'res_raw_11142141'!$E$4,'res_raw_11142141'!$E$5)=0,'res_raw_11142141'!$E$6,SUM(C5:C8))</f>
         <v/>
       </c>
       <c r="D9" s="27">
-        <f>SUM(D5:D8)</f>
+        <f>IF(COUNT('res_raw_11142141'!$D$2,'res_raw_11142141'!$D$3,'res_raw_11142141'!$D$4,'res_raw_11142141'!$D$5)=0,'res_raw_11142141'!$D$6,SUM(D5:D8))</f>
         <v/>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>Beregnet: Nettoomsætning + Andre driftsindt. − Vareforbrug − Andre ext. omk.</t>
+          <t>Beregnet: Nettoomsætning + Andre driftsindt. − Vareforbrug − Andre ext. omk. Er komponenterne ikke indberettet, vises rapporteret bruttoresultat (fsa:GrossResult) direkte.</t>
         </is>
       </c>
     </row>

--- a/filer_2/11142141_nordic_seafood_a_s.xlsx
+++ b/filer_2/11142141_nordic_seafood_a_s.xlsx
@@ -6687,15 +6687,15 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>IF(COUNT('res_raw_11142141'!$F$2,'res_raw_11142141'!$F$3,'res_raw_11142141'!$F$4,'res_raw_11142141'!$F$5)=0,'res_raw_11142141'!$F$6,SUM(B5:B8))</f>
+        <f>IF(ABS((SUM(B5:B8))-'res_raw_11142141'!$F$6)&lt;=2,SUM(B5:B8),'res_raw_11142141'!$F$6)</f>
         <v/>
       </c>
       <c r="C9" s="27">
-        <f>IF(COUNT('res_raw_11142141'!$E$2,'res_raw_11142141'!$E$3,'res_raw_11142141'!$E$4,'res_raw_11142141'!$E$5)=0,'res_raw_11142141'!$E$6,SUM(C5:C8))</f>
+        <f>IF(ABS((SUM(C5:C8))-'res_raw_11142141'!$E$6)&lt;=2,SUM(C5:C8),'res_raw_11142141'!$E$6)</f>
         <v/>
       </c>
       <c r="D9" s="27">
-        <f>IF(COUNT('res_raw_11142141'!$D$2,'res_raw_11142141'!$D$3,'res_raw_11142141'!$D$4,'res_raw_11142141'!$D$5)=0,'res_raw_11142141'!$D$6,SUM(D5:D8))</f>
+        <f>IF(ABS((SUM(D5:D8))-'res_raw_11142141'!$D$6)&lt;=2,SUM(D5:D8),'res_raw_11142141'!$D$6)</f>
         <v/>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -6783,15 +6783,15 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(B9:B12)</f>
+        <f>IF(ABS((SUM(B9:B12))-'res_raw_11142141'!$F$11)&lt;=2,SUM(B9:B12),'res_raw_11142141'!$F$11)</f>
         <v/>
       </c>
       <c r="C13" s="27">
-        <f>SUM(C9:C12)</f>
+        <f>IF(ABS((SUM(C9:C12))-'res_raw_11142141'!$E$11)&lt;=2,SUM(C9:C12),'res_raw_11142141'!$E$11)</f>
         <v/>
       </c>
       <c r="D13" s="27">
-        <f>SUM(D9:D12)</f>
+        <f>IF(ABS((SUM(D9:D12))-'res_raw_11142141'!$D$11)&lt;=2,SUM(D9:D12),'res_raw_11142141'!$D$11)</f>
         <v/>
       </c>
       <c r="F13" s="28" t="inlineStr">
@@ -6855,15 +6855,15 @@
         </is>
       </c>
       <c r="B16" s="27">
-        <f>SUM(B13:B15)</f>
+        <f>IF(ABS((SUM(B13:B15))-'res_raw_11142141'!$F$16)&lt;=2,SUM(B13:B15),'res_raw_11142141'!$F$16)</f>
         <v/>
       </c>
       <c r="C16" s="27">
-        <f>SUM(C13:C15)</f>
+        <f>IF(ABS((SUM(C13:C15))-'res_raw_11142141'!$E$16)&lt;=2,SUM(C13:C15),'res_raw_11142141'!$E$16)</f>
         <v/>
       </c>
       <c r="D16" s="27">
-        <f>SUM(D13:D15)</f>
+        <f>IF(ABS((SUM(D13:D15))-'res_raw_11142141'!$D$16)&lt;=2,SUM(D13:D15),'res_raw_11142141'!$D$16)</f>
         <v/>
       </c>
       <c r="F16" s="28" t="inlineStr">

--- a/filer_2/11142141_nordic_seafood_a_s.xlsx
+++ b/filer_2/11142141_nordic_seafood_a_s.xlsx
@@ -5189,8 +5189,12 @@
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
+      <c r="B15" s="17" t="n">
+        <v>-6908</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>-14808</v>
+      </c>
       <c r="D15" s="17" t="n">
         <v>-26496</v>
       </c>
